--- a/src/production/PickAndPlace.xlsx
+++ b/src/production/PickAndPlace.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="PickAndPlace_PCB1_2025-11-09" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="PickAndPlace_PCB1_2026-01-31" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1622" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1754" uniqueCount="560">
   <si>
     <t>Designator</t>
   </si>
@@ -157,13 +157,13 @@
     <t>TF-SMD_TF-110</t>
   </si>
   <si>
-    <t>58.166mm</t>
+    <t>58.162mm</t>
   </si>
   <si>
     <t>16.256mm</t>
   </si>
   <si>
-    <t>61.621mm</t>
+    <t>61.618mm</t>
   </si>
   <si>
     <t>19.474mm</t>
@@ -277,1351 +277,1420 @@
     <t>SCREW2</t>
   </si>
   <si>
+    <t>D5</t>
+  </si>
+  <si>
+    <t>RClamp0524PATCT_C40960</t>
+  </si>
+  <si>
+    <t>SLP2510P8_L2.5-W1.0-P0.50-BL</t>
+  </si>
+  <si>
+    <t>49.76mm</t>
+  </si>
+  <si>
+    <t>17.87mm</t>
+  </si>
+  <si>
+    <t>49.32mm</t>
+  </si>
+  <si>
+    <t>18.87mm</t>
+  </si>
+  <si>
+    <t>RClamp0524PATCT</t>
+  </si>
+  <si>
+    <t>D7</t>
+  </si>
+  <si>
+    <t>13.02mm</t>
+  </si>
+  <si>
+    <t>14.02mm</t>
+  </si>
+  <si>
+    <t>D8</t>
+  </si>
+  <si>
+    <t>14.52mm</t>
+  </si>
+  <si>
+    <t>8.85mm</t>
+  </si>
+  <si>
+    <t>13.52mm</t>
+  </si>
+  <si>
+    <t>8.41mm</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>AFC07-S22FCC-00</t>
+  </si>
+  <si>
+    <t>FPC-SMD_AFC07-S22FCC-00</t>
+  </si>
+  <si>
+    <t>4mm</t>
+  </si>
+  <si>
+    <t>15.5mm</t>
+  </si>
+  <si>
+    <t>5.129mm</t>
+  </si>
+  <si>
+    <t>10.255mm</t>
+  </si>
+  <si>
+    <t>X4</t>
+  </si>
+  <si>
+    <t>7R24000E12UBE</t>
+  </si>
+  <si>
+    <t>CRYSTAL-SMD_4P-L1.6-W1.2-BL</t>
+  </si>
+  <si>
+    <t>20.88mm</t>
+  </si>
+  <si>
+    <t>4.09mm</t>
+  </si>
+  <si>
+    <t>21.43mm</t>
+  </si>
+  <si>
+    <t>4.49mm</t>
+  </si>
+  <si>
+    <t>24MHz</t>
+  </si>
+  <si>
+    <t>D6</t>
+  </si>
+  <si>
+    <t>11.53mm</t>
+  </si>
+  <si>
+    <t>10.53mm</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t>FTC201210S2R2MBCA</t>
+  </si>
+  <si>
+    <t>IND-SMD_L2.0-W1.2_FTC201210S</t>
+  </si>
+  <si>
+    <t>44.624mm</t>
+  </si>
+  <si>
+    <t>7.747mm</t>
+  </si>
+  <si>
+    <t>8.397mm</t>
+  </si>
+  <si>
+    <t>2.2uH</t>
+  </si>
+  <si>
+    <t>L2</t>
+  </si>
+  <si>
+    <t>46.85mm</t>
+  </si>
+  <si>
+    <t>2.91mm</t>
+  </si>
+  <si>
+    <t>2.26mm</t>
+  </si>
+  <si>
+    <t>L3</t>
+  </si>
+  <si>
+    <t>40.79mm</t>
+  </si>
+  <si>
+    <t>L4</t>
+  </si>
+  <si>
+    <t>PBY100505T-101Y-N</t>
+  </si>
+  <si>
+    <t>L0402</t>
+  </si>
+  <si>
+    <t>18.26mm</t>
+  </si>
+  <si>
+    <t>7mm</t>
+  </si>
+  <si>
+    <t>18.805mm</t>
+  </si>
+  <si>
+    <t>L5</t>
+  </si>
+  <si>
+    <t>7.315mm</t>
+  </si>
+  <si>
+    <t>9.369mm</t>
+  </si>
+  <si>
+    <t>8.823mm</t>
+  </si>
+  <si>
+    <t>L6</t>
+  </si>
+  <si>
+    <t>18.83mm</t>
+  </si>
+  <si>
+    <t>8.99mm</t>
+  </si>
+  <si>
+    <t>8.445mm</t>
+  </si>
+  <si>
+    <t>1V2</t>
+  </si>
+  <si>
+    <t>Test-Point</t>
+  </si>
+  <si>
+    <t>Test-Point-0.5mm</t>
+  </si>
+  <si>
+    <t>34.874mm</t>
+  </si>
+  <si>
+    <t>3.553mm</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>1V8</t>
+  </si>
+  <si>
+    <t>25.338mm</t>
+  </si>
+  <si>
+    <t>5.443mm</t>
+  </si>
+  <si>
+    <t>3V3</t>
+  </si>
+  <si>
+    <t>25.32mm</t>
+  </si>
+  <si>
+    <t>8.123mm</t>
+  </si>
+  <si>
+    <t>5V</t>
+  </si>
+  <si>
+    <t>47.648mm</t>
+  </si>
+  <si>
+    <t>7.713mm</t>
+  </si>
+  <si>
+    <t>VBUS</t>
+  </si>
+  <si>
+    <t>57.088mm</t>
+  </si>
+  <si>
+    <t>8.073mm</t>
+  </si>
+  <si>
+    <t>GND</t>
+  </si>
+  <si>
+    <t>45.41mm</t>
+  </si>
+  <si>
+    <t>10.49mm</t>
+  </si>
+  <si>
+    <t>D+</t>
+  </si>
+  <si>
+    <t>51.786mm</t>
+  </si>
+  <si>
+    <t>3.145mm</t>
+  </si>
+  <si>
+    <t>D-</t>
+  </si>
+  <si>
+    <t>54.59mm</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>GRM0335C1E221JA01D</t>
+  </si>
+  <si>
+    <t>C0201</t>
+  </si>
+  <si>
+    <t>43.114mm</t>
+  </si>
+  <si>
+    <t>7.457mm</t>
+  </si>
+  <si>
+    <t>7.731mm</t>
+  </si>
+  <si>
+    <t>220pF</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>45.47mm</t>
+  </si>
+  <si>
+    <t>1.78mm</t>
+  </si>
+  <si>
+    <t>2.054mm</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>GRM155R61A106ME44D</t>
+  </si>
+  <si>
+    <t>C0402</t>
+  </si>
+  <si>
+    <t>47.02mm</t>
+  </si>
+  <si>
+    <t>1.3mm</t>
+  </si>
+  <si>
+    <t>46.475mm</t>
+  </si>
+  <si>
+    <t>10uF</t>
+  </si>
+  <si>
+    <t>C5</t>
+  </si>
+  <si>
+    <t>41.45mm</t>
+  </si>
+  <si>
+    <t>1.37mm</t>
+  </si>
+  <si>
+    <t>41.176mm</t>
+  </si>
+  <si>
+    <t>C6</t>
+  </si>
+  <si>
+    <t>40.07mm</t>
+  </si>
+  <si>
+    <t>40.615mm</t>
+  </si>
+  <si>
+    <t>C7</t>
+  </si>
+  <si>
+    <t>46.704mm</t>
+  </si>
+  <si>
+    <t>5.347mm</t>
+  </si>
+  <si>
+    <t>46.159mm</t>
+  </si>
+  <si>
+    <t>C8</t>
+  </si>
+  <si>
+    <t>46.699mm</t>
+  </si>
+  <si>
+    <t>4.571mm</t>
+  </si>
+  <si>
+    <t>46.154mm</t>
+  </si>
+  <si>
+    <t>C9</t>
+  </si>
+  <si>
+    <t>40.531mm</t>
+  </si>
+  <si>
+    <t>5.023mm</t>
+  </si>
+  <si>
+    <t>41.076mm</t>
+  </si>
+  <si>
+    <t>C14</t>
+  </si>
+  <si>
+    <t>GRM033R61A104KE15D</t>
+  </si>
+  <si>
+    <t>21.49mm</t>
+  </si>
+  <si>
+    <t>12.4mm</t>
+  </si>
+  <si>
+    <t>21.764mm</t>
+  </si>
+  <si>
+    <t>100nF</t>
+  </si>
+  <si>
+    <t>C15</t>
+  </si>
+  <si>
+    <t>9.4mm</t>
+  </si>
+  <si>
+    <t>C16</t>
+  </si>
+  <si>
+    <t>39.89mm</t>
+  </si>
+  <si>
+    <t>39.616mm</t>
+  </si>
+  <si>
+    <t>C17</t>
+  </si>
+  <si>
+    <t>19.29mm</t>
+  </si>
+  <si>
+    <t>C18</t>
+  </si>
+  <si>
+    <t>11.41mm</t>
+  </si>
+  <si>
+    <t>C19</t>
+  </si>
+  <si>
+    <t>16.17mm</t>
+  </si>
+  <si>
+    <t>C20</t>
+  </si>
+  <si>
+    <t>32.44mm</t>
+  </si>
+  <si>
+    <t>3.6mm</t>
+  </si>
+  <si>
+    <t>3.874mm</t>
+  </si>
+  <si>
+    <t>C21</t>
+  </si>
+  <si>
+    <t>39.49mm</t>
+  </si>
+  <si>
+    <t>6.72mm</t>
+  </si>
+  <si>
+    <t>6.994mm</t>
+  </si>
+  <si>
+    <t>C22</t>
+  </si>
+  <si>
+    <t>29.06mm</t>
+  </si>
+  <si>
+    <t>C23</t>
+  </si>
+  <si>
+    <t>28.99mm</t>
+  </si>
+  <si>
+    <t>22.16mm</t>
+  </si>
+  <si>
+    <t>21.886mm</t>
+  </si>
+  <si>
+    <t>C24</t>
+  </si>
+  <si>
+    <t>28.21mm</t>
+  </si>
+  <si>
+    <t>C25</t>
+  </si>
+  <si>
+    <t>27.43mm</t>
+  </si>
+  <si>
+    <t>C26</t>
+  </si>
+  <si>
+    <t>26.65mm</t>
+  </si>
+  <si>
+    <t>C27</t>
+  </si>
+  <si>
+    <t>13.4mm</t>
+  </si>
+  <si>
+    <t>C28</t>
+  </si>
+  <si>
+    <t>17.01mm</t>
+  </si>
+  <si>
+    <t>C29</t>
+  </si>
+  <si>
+    <t>11.62mm</t>
+  </si>
+  <si>
+    <t>C30</t>
+  </si>
+  <si>
+    <t>10.18mm</t>
+  </si>
+  <si>
+    <t>C31</t>
+  </si>
+  <si>
+    <t>21.48mm</t>
+  </si>
+  <si>
+    <t>6.27mm</t>
+  </si>
+  <si>
+    <t>21.754mm</t>
+  </si>
+  <si>
+    <t>C32</t>
+  </si>
+  <si>
+    <t>30.62mm</t>
+  </si>
+  <si>
+    <t>C33</t>
+  </si>
+  <si>
+    <t>8.62mm</t>
+  </si>
+  <si>
+    <t>C34</t>
+  </si>
+  <si>
+    <t>29.77mm</t>
+  </si>
+  <si>
+    <t>22.12mm</t>
+  </si>
+  <si>
+    <t>21.846mm</t>
+  </si>
+  <si>
+    <t>C37</t>
+  </si>
+  <si>
+    <t>18.51mm</t>
+  </si>
+  <si>
+    <t>C38</t>
+  </si>
+  <si>
+    <t>10.63mm</t>
+  </si>
+  <si>
+    <t>C39</t>
+  </si>
+  <si>
+    <t>21.478mm</t>
+  </si>
+  <si>
+    <t>7.835mm</t>
+  </si>
+  <si>
+    <t>21.753mm</t>
+  </si>
+  <si>
+    <t>C40</t>
+  </si>
+  <si>
+    <t>7.05mm</t>
+  </si>
+  <si>
+    <t>C41</t>
+  </si>
+  <si>
+    <t>23.56mm</t>
+  </si>
+  <si>
+    <t>C44</t>
+  </si>
+  <si>
+    <t>41.08mm</t>
+  </si>
+  <si>
+    <t>17.77mm</t>
+  </si>
+  <si>
+    <t>17.225mm</t>
+  </si>
+  <si>
+    <t>C45</t>
+  </si>
+  <si>
+    <t>16.96mm</t>
+  </si>
+  <si>
+    <t>C46</t>
+  </si>
+  <si>
+    <t>38.24mm</t>
+  </si>
+  <si>
+    <t>5.17mm</t>
+  </si>
+  <si>
+    <t>5.715mm</t>
+  </si>
+  <si>
+    <t>C47</t>
+  </si>
+  <si>
+    <t>41.1mm</t>
+  </si>
+  <si>
+    <t>13.54mm</t>
+  </si>
+  <si>
+    <t>40.555mm</t>
+  </si>
+  <si>
+    <t>C48</t>
+  </si>
+  <si>
+    <t>39.53mm</t>
+  </si>
+  <si>
+    <t>13.53mm</t>
+  </si>
+  <si>
+    <t>13.804mm</t>
+  </si>
+  <si>
+    <t>C49</t>
+  </si>
+  <si>
+    <t>41.12mm</t>
+  </si>
+  <si>
+    <t>15.4mm</t>
+  </si>
+  <si>
+    <t>14.855mm</t>
+  </si>
+  <si>
+    <t>C51</t>
+  </si>
+  <si>
+    <t>25.16mm</t>
+  </si>
+  <si>
+    <t>C52</t>
+  </si>
+  <si>
+    <t>27.5mm</t>
+  </si>
+  <si>
+    <t>C53</t>
+  </si>
+  <si>
+    <t>GRM0335C1H150JA01D</t>
+  </si>
+  <si>
+    <t>22.52mm</t>
+  </si>
+  <si>
+    <t>3.8mm</t>
+  </si>
+  <si>
+    <t>3.526mm</t>
+  </si>
+  <si>
+    <t>15pF</t>
+  </si>
+  <si>
+    <t>C54</t>
+  </si>
+  <si>
+    <t>19.24mm</t>
+  </si>
+  <si>
+    <t>3.83mm</t>
+  </si>
+  <si>
+    <t>3.556mm</t>
+  </si>
+  <si>
+    <t>C55</t>
+  </si>
+  <si>
+    <t>38.01mm</t>
+  </si>
+  <si>
+    <t>1.156mm</t>
+  </si>
+  <si>
+    <t>C56</t>
+  </si>
+  <si>
+    <t>33.84mm</t>
+  </si>
+  <si>
+    <t>C58</t>
+  </si>
+  <si>
+    <t>50.229mm</t>
+  </si>
+  <si>
+    <t>9.93mm</t>
+  </si>
+  <si>
+    <t>9.655mm</t>
+  </si>
+  <si>
+    <t>C59</t>
+  </si>
+  <si>
+    <t>46.7mm</t>
+  </si>
+  <si>
+    <t>6.13mm</t>
+  </si>
+  <si>
+    <t>46.426mm</t>
+  </si>
+  <si>
+    <t>C60</t>
+  </si>
+  <si>
+    <t>10.39mm</t>
+  </si>
+  <si>
+    <t>10.664mm</t>
+  </si>
+  <si>
+    <t>C61</t>
+  </si>
+  <si>
+    <t>14.53mm</t>
+  </si>
+  <si>
+    <t>10.41mm</t>
+  </si>
+  <si>
+    <t>10.684mm</t>
+  </si>
+  <si>
+    <t>C62</t>
+  </si>
+  <si>
+    <t>19.32mm</t>
+  </si>
+  <si>
+    <t>14.39mm</t>
+  </si>
+  <si>
+    <t>19.046mm</t>
+  </si>
+  <si>
+    <t>C63</t>
+  </si>
+  <si>
+    <t>19.33mm</t>
+  </si>
+  <si>
+    <t>17.64mm</t>
+  </si>
+  <si>
+    <t>19.056mm</t>
+  </si>
+  <si>
+    <t>C64</t>
+  </si>
+  <si>
+    <t>14.03mm</t>
+  </si>
+  <si>
+    <t>22.48mm</t>
+  </si>
+  <si>
+    <t>22.206mm</t>
+  </si>
+  <si>
+    <t>C65</t>
+  </si>
+  <si>
+    <t>7.22mm</t>
+  </si>
+  <si>
+    <t>18.14mm</t>
+  </si>
+  <si>
+    <t>7.494mm</t>
+  </si>
+  <si>
+    <t>C66</t>
+  </si>
+  <si>
+    <t>15.7mm</t>
+  </si>
+  <si>
+    <t>C67</t>
+  </si>
+  <si>
+    <t>12.64mm</t>
+  </si>
+  <si>
+    <t>C68</t>
+  </si>
+  <si>
+    <t>C69</t>
+  </si>
+  <si>
+    <t>16.53mm</t>
+  </si>
+  <si>
+    <t>22.46mm</t>
+  </si>
+  <si>
+    <t>22.186mm</t>
+  </si>
+  <si>
+    <t>C70</t>
+  </si>
+  <si>
+    <t>16.48mm</t>
+  </si>
+  <si>
+    <t>C71</t>
+  </si>
+  <si>
+    <t>19.82mm</t>
+  </si>
+  <si>
+    <t>6.71mm</t>
+  </si>
+  <si>
+    <t>6.984mm</t>
+  </si>
+  <si>
+    <t>C72</t>
+  </si>
+  <si>
+    <t>17.83mm</t>
+  </si>
+  <si>
+    <t>8.68mm</t>
+  </si>
+  <si>
+    <t>8.135mm</t>
+  </si>
+  <si>
+    <t>C73</t>
+  </si>
+  <si>
+    <t>6.428mm</t>
+  </si>
+  <si>
+    <t>8.858mm</t>
+  </si>
+  <si>
+    <t>8.313mm</t>
+  </si>
+  <si>
+    <t>C74</t>
+  </si>
+  <si>
+    <t>19.72mm</t>
+  </si>
+  <si>
+    <t>8.94mm</t>
+  </si>
+  <si>
+    <t>8.666mm</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>42.824mm</t>
+  </si>
+  <si>
+    <t>8.537mm</t>
+  </si>
+  <si>
+    <t>43.369mm</t>
+  </si>
+  <si>
+    <t>C10</t>
+  </si>
+  <si>
+    <t>GRM033R61A105ME44D</t>
+  </si>
+  <si>
+    <t>41.014mm</t>
+  </si>
+  <si>
+    <t>5.917mm</t>
+  </si>
+  <si>
+    <t>41.288mm</t>
+  </si>
+  <si>
+    <t>1uF</t>
+  </si>
+  <si>
+    <t>C42</t>
+  </si>
+  <si>
+    <t>24.379mm</t>
+  </si>
+  <si>
+    <t>C43</t>
+  </si>
+  <si>
+    <t>29.84mm</t>
+  </si>
+  <si>
+    <t>C50</t>
+  </si>
+  <si>
+    <t>14.61mm</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>0201WMF6802TEE</t>
+  </si>
+  <si>
+    <t>R0201</t>
+  </si>
+  <si>
+    <t>42.329mm</t>
+  </si>
+  <si>
+    <t>7.392mm</t>
+  </si>
+  <si>
+    <t>7.15mm</t>
+  </si>
+  <si>
+    <t>68kΩ</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>0201WMF1502TEE</t>
+  </si>
+  <si>
+    <t>41.539mm</t>
+  </si>
+  <si>
+    <t>15kΩ</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>0201WMF2003TEE</t>
+  </si>
+  <si>
+    <t>44.46mm</t>
+  </si>
+  <si>
+    <t>2.2mm</t>
+  </si>
+  <si>
+    <t>44.218mm</t>
+  </si>
+  <si>
+    <t>200kΩ</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>0201WMF1003TEE</t>
+  </si>
+  <si>
+    <t>100kΩ</t>
+  </si>
+  <si>
+    <t>R5</t>
+  </si>
+  <si>
+    <t>43.22mm</t>
+  </si>
+  <si>
+    <t>43.461mm</t>
+  </si>
+  <si>
+    <t>R6</t>
+  </si>
+  <si>
+    <t>R8</t>
+  </si>
+  <si>
+    <t>0201WMF2400TEE</t>
+  </si>
+  <si>
+    <t>28.28mm</t>
+  </si>
+  <si>
+    <t>3.665mm</t>
+  </si>
+  <si>
+    <t>3.907mm</t>
+  </si>
+  <si>
+    <t>240Ω</t>
+  </si>
+  <si>
+    <t>R9</t>
+  </si>
+  <si>
+    <t>15.39mm</t>
+  </si>
+  <si>
+    <t>40.131mm</t>
+  </si>
+  <si>
+    <t>R10</t>
+  </si>
+  <si>
+    <t>0201WMF2001TEE</t>
+  </si>
+  <si>
+    <t>25.94mm</t>
+  </si>
+  <si>
+    <t>2kΩ</t>
+  </si>
+  <si>
+    <t>R11</t>
+  </si>
+  <si>
+    <t>26.72mm</t>
+  </si>
+  <si>
+    <t>3.424mm</t>
+  </si>
+  <si>
+    <t>R12</t>
+  </si>
+  <si>
+    <t>0201WMF1005TEE</t>
+  </si>
+  <si>
+    <t>36.65mm</t>
+  </si>
+  <si>
+    <t>3.89mm</t>
+  </si>
+  <si>
+    <t>36.408mm</t>
+  </si>
+  <si>
+    <t>10MΩ</t>
+  </si>
+  <si>
+    <t>R13</t>
+  </si>
+  <si>
+    <t>0201WMF4702TEE</t>
+  </si>
+  <si>
+    <t>48.54mm</t>
+  </si>
+  <si>
+    <t>19.13mm</t>
+  </si>
+  <si>
+    <t>18.888mm</t>
+  </si>
+  <si>
+    <t>47kΩ</t>
+  </si>
+  <si>
+    <t>R14</t>
+  </si>
+  <si>
+    <t>51.77mm</t>
+  </si>
+  <si>
+    <t>18.08mm</t>
+  </si>
+  <si>
+    <t>18.322mm</t>
+  </si>
+  <si>
+    <t>R15</t>
+  </si>
+  <si>
+    <t>17.67mm</t>
+  </si>
+  <si>
+    <t>17.428mm</t>
+  </si>
+  <si>
+    <t>R16</t>
+  </si>
+  <si>
+    <t>48.38mm</t>
+  </si>
+  <si>
+    <t>14.31mm</t>
+  </si>
+  <si>
+    <t>14.068mm</t>
+  </si>
+  <si>
+    <t>R17</t>
+  </si>
+  <si>
+    <t>51.07mm</t>
+  </si>
+  <si>
+    <t>13.24mm</t>
+  </si>
+  <si>
+    <t>13.482mm</t>
+  </si>
+  <si>
+    <t>R18</t>
+  </si>
+  <si>
+    <t>0201WMF330JTEE</t>
+  </si>
+  <si>
+    <t>51.21mm</t>
+  </si>
+  <si>
+    <t>16.87mm</t>
+  </si>
+  <si>
+    <t>51.451mm</t>
+  </si>
+  <si>
+    <t>33Ω</t>
+  </si>
+  <si>
+    <t>R19</t>
+  </si>
+  <si>
+    <t>0201WMF4701TEE</t>
+  </si>
+  <si>
+    <t>11.84mm</t>
+  </si>
+  <si>
+    <t>19.078mm</t>
+  </si>
+  <si>
+    <t>4.7kΩ</t>
+  </si>
+  <si>
+    <t>R20</t>
+  </si>
+  <si>
+    <t>12.62mm</t>
+  </si>
+  <si>
+    <t>R21</t>
+  </si>
+  <si>
+    <t>0201WMF2201TEE</t>
+  </si>
+  <si>
+    <t>7.285mm</t>
+  </si>
+  <si>
+    <t>14.92mm</t>
+  </si>
+  <si>
+    <t>7.527mm</t>
+  </si>
+  <si>
+    <t>2.2kΩ</t>
+  </si>
+  <si>
+    <t>R22</t>
+  </si>
+  <si>
+    <t>14.14mm</t>
+  </si>
+  <si>
+    <t>R23</t>
+  </si>
+  <si>
+    <t>0201WMF4301TEE</t>
+  </si>
+  <si>
+    <t>9.79mm</t>
+  </si>
+  <si>
+    <t>10.58mm</t>
+  </si>
+  <si>
+    <t>9.548mm</t>
+  </si>
+  <si>
+    <t>4.3kΩ</t>
+  </si>
+  <si>
+    <t>R24</t>
+  </si>
+  <si>
+    <t>0201WMF1002TEE</t>
+  </si>
+  <si>
+    <t>11.86mm</t>
+  </si>
+  <si>
+    <t>10kΩ</t>
+  </si>
+  <si>
+    <t>R25</t>
+  </si>
+  <si>
+    <t>17.843mm</t>
+  </si>
+  <si>
+    <t>10.453mm</t>
+  </si>
+  <si>
+    <t>10.694mm</t>
+  </si>
+  <si>
+    <t>R26</t>
+  </si>
+  <si>
+    <t>0201WMF5101TEE</t>
+  </si>
+  <si>
+    <t>52.107mm</t>
+  </si>
+  <si>
+    <t>7.729mm</t>
+  </si>
+  <si>
+    <t>7.97mm</t>
+  </si>
+  <si>
+    <t>5.1kΩ</t>
+  </si>
+  <si>
+    <t>R27</t>
+  </si>
+  <si>
+    <t>55.098mm</t>
+  </si>
+  <si>
+    <t>R36</t>
+  </si>
+  <si>
+    <t>0201WMF220JTEE</t>
+  </si>
+  <si>
+    <t>41.52mm</t>
+  </si>
+  <si>
+    <t>12.44mm</t>
+  </si>
+  <si>
+    <t>41.761mm</t>
+  </si>
+  <si>
+    <t>22Ω</t>
+  </si>
+  <si>
+    <t>R37</t>
+  </si>
+  <si>
+    <t>11.65mm</t>
+  </si>
+  <si>
+    <t>3V0</t>
+  </si>
+  <si>
+    <t>43.692mm</t>
+  </si>
+  <si>
+    <t>14.362mm</t>
+  </si>
+  <si>
+    <t>C82</t>
+  </si>
+  <si>
+    <t>46.88mm</t>
+  </si>
+  <si>
+    <t>14.25mm</t>
+  </si>
+  <si>
+    <t>13.976mm</t>
+  </si>
+  <si>
+    <t>C83</t>
+  </si>
+  <si>
+    <t>42.18mm</t>
+  </si>
+  <si>
+    <t>14.95mm</t>
+  </si>
+  <si>
+    <t>14.676mm</t>
+  </si>
+  <si>
+    <t>U9</t>
+  </si>
+  <si>
+    <t>LP5907MFX-3.3/NOPB</t>
+  </si>
+  <si>
+    <t>SOT-23-5_L3.0-W1.7-P0.95-LS2.8-BR</t>
+  </si>
+  <si>
+    <t>44.54mm</t>
+  </si>
+  <si>
+    <t>14.7mm</t>
+  </si>
+  <si>
+    <t>45.84mm</t>
+  </si>
+  <si>
+    <t>13.75mm</t>
+  </si>
+  <si>
+    <t>AV</t>
+  </si>
+  <si>
+    <t>16.494mm</t>
+  </si>
+  <si>
+    <t>7.503mm</t>
+  </si>
+  <si>
+    <t>CLK</t>
+  </si>
+  <si>
+    <t>15.089mm</t>
+  </si>
+  <si>
+    <t>CMD</t>
+  </si>
+  <si>
+    <t>17.279mm</t>
+  </si>
+  <si>
+    <t>CV</t>
+  </si>
+  <si>
+    <t>19.114mm</t>
+  </si>
+  <si>
+    <t>10.529mm</t>
+  </si>
+  <si>
+    <t>D0</t>
+  </si>
+  <si>
+    <t>12.869mm</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>11.789mm</t>
+  </si>
+  <si>
     <t>D2</t>
   </si>
   <si>
-    <t>RClamp0524PATCT_C40960</t>
-  </si>
-  <si>
-    <t>SLP2510P8_L2.5-W1.0-P0.50-BL</t>
-  </si>
-  <si>
-    <t>49.76mm</t>
-  </si>
-  <si>
-    <t>17.87mm</t>
-  </si>
-  <si>
-    <t>49.32mm</t>
-  </si>
-  <si>
-    <t>18.87mm</t>
-  </si>
-  <si>
-    <t>RClamp0524PATCT</t>
+    <t>61.632mm</t>
+  </si>
+  <si>
+    <t>19.473mm</t>
   </si>
   <si>
     <t>D3</t>
   </si>
   <si>
-    <t>13.02mm</t>
-  </si>
-  <si>
-    <t>14.02mm</t>
-  </si>
-  <si>
-    <t>D4</t>
-  </si>
-  <si>
-    <t>14.52mm</t>
-  </si>
-  <si>
-    <t>8.85mm</t>
-  </si>
-  <si>
-    <t>13.52mm</t>
-  </si>
-  <si>
-    <t>8.41mm</t>
-  </si>
-  <si>
-    <t>P1</t>
-  </si>
-  <si>
-    <t>AFC07-S22FCC-00</t>
-  </si>
-  <si>
-    <t>FPC-SMD_AFC07-S22FCC-00</t>
-  </si>
-  <si>
-    <t>4mm</t>
-  </si>
-  <si>
-    <t>15.5mm</t>
-  </si>
-  <si>
-    <t>5.129mm</t>
-  </si>
-  <si>
-    <t>10.255mm</t>
-  </si>
-  <si>
-    <t>X4</t>
-  </si>
-  <si>
-    <t>7R24000E12UBE</t>
-  </si>
-  <si>
-    <t>CRYSTAL-SMD_4P-L1.6-W1.2-BL</t>
-  </si>
-  <si>
-    <t>20.88mm</t>
-  </si>
-  <si>
-    <t>4.09mm</t>
-  </si>
-  <si>
-    <t>21.43mm</t>
-  </si>
-  <si>
-    <t>4.49mm</t>
-  </si>
-  <si>
-    <t>24MHz</t>
-  </si>
-  <si>
-    <t>D5</t>
-  </si>
-  <si>
-    <t>11.53mm</t>
-  </si>
-  <si>
-    <t>10.53mm</t>
-  </si>
-  <si>
-    <t>L1</t>
-  </si>
-  <si>
-    <t>FTC201210S2R2MBCA</t>
-  </si>
-  <si>
-    <t>IND-SMD_L2.0-W1.2_FTC201210S</t>
-  </si>
-  <si>
-    <t>44.624mm</t>
-  </si>
-  <si>
-    <t>7.747mm</t>
-  </si>
-  <si>
-    <t>8.397mm</t>
-  </si>
-  <si>
-    <t>2.2uH</t>
-  </si>
-  <si>
-    <t>L2</t>
-  </si>
-  <si>
-    <t>46.85mm</t>
-  </si>
-  <si>
-    <t>2.91mm</t>
-  </si>
-  <si>
-    <t>2.26mm</t>
-  </si>
-  <si>
-    <t>L3</t>
-  </si>
-  <si>
-    <t>40.79mm</t>
-  </si>
-  <si>
-    <t>L4</t>
-  </si>
-  <si>
-    <t>PBY100505T-101Y-N</t>
-  </si>
-  <si>
-    <t>L0402</t>
-  </si>
-  <si>
-    <t>18.26mm</t>
-  </si>
-  <si>
-    <t>7mm</t>
-  </si>
-  <si>
-    <t>18.805mm</t>
-  </si>
-  <si>
-    <t>L5</t>
-  </si>
-  <si>
-    <t>7.315mm</t>
-  </si>
-  <si>
-    <t>9.369mm</t>
-  </si>
-  <si>
-    <t>8.823mm</t>
-  </si>
-  <si>
-    <t>L6</t>
-  </si>
-  <si>
-    <t>18.83mm</t>
-  </si>
-  <si>
-    <t>8.99mm</t>
-  </si>
-  <si>
-    <t>8.445mm</t>
-  </si>
-  <si>
-    <t>1V2</t>
-  </si>
-  <si>
-    <t>Test-Point</t>
-  </si>
-  <si>
-    <t>Test-Point-0.5mm</t>
-  </si>
-  <si>
-    <t>34.874mm</t>
-  </si>
-  <si>
-    <t>3.553mm</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>1V8</t>
-  </si>
-  <si>
-    <t>25.338mm</t>
-  </si>
-  <si>
-    <t>5.443mm</t>
-  </si>
-  <si>
-    <t>3V3</t>
-  </si>
-  <si>
-    <t>25.32mm</t>
-  </si>
-  <si>
-    <t>8.123mm</t>
-  </si>
-  <si>
-    <t>5V</t>
-  </si>
-  <si>
-    <t>47.648mm</t>
-  </si>
-  <si>
-    <t>7.713mm</t>
-  </si>
-  <si>
-    <t>VBUS</t>
-  </si>
-  <si>
-    <t>57.088mm</t>
-  </si>
-  <si>
-    <t>8.073mm</t>
-  </si>
-  <si>
-    <t>GND</t>
-  </si>
-  <si>
-    <t>45.41mm</t>
-  </si>
-  <si>
-    <t>10.49mm</t>
-  </si>
-  <si>
-    <t>D+</t>
-  </si>
-  <si>
-    <t>51.786mm</t>
-  </si>
-  <si>
-    <t>3.145mm</t>
-  </si>
-  <si>
-    <t>D-</t>
-  </si>
-  <si>
-    <t>54.59mm</t>
-  </si>
-  <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>GRM0335C1E221JA01D</t>
-  </si>
-  <si>
-    <t>C0201</t>
-  </si>
-  <si>
-    <t>43.114mm</t>
-  </si>
-  <si>
-    <t>7.457mm</t>
-  </si>
-  <si>
-    <t>7.731mm</t>
-  </si>
-  <si>
-    <t>220pF</t>
-  </si>
-  <si>
-    <t>C3</t>
-  </si>
-  <si>
-    <t>45.47mm</t>
-  </si>
-  <si>
-    <t>1.78mm</t>
-  </si>
-  <si>
-    <t>2.054mm</t>
-  </si>
-  <si>
-    <t>C4</t>
-  </si>
-  <si>
-    <t>GRM155R61A106ME44D</t>
-  </si>
-  <si>
-    <t>C0402</t>
-  </si>
-  <si>
-    <t>47.02mm</t>
-  </si>
-  <si>
-    <t>1.3mm</t>
-  </si>
-  <si>
-    <t>46.475mm</t>
-  </si>
-  <si>
-    <t>10uF</t>
-  </si>
-  <si>
-    <t>C5</t>
-  </si>
-  <si>
-    <t>41.45mm</t>
-  </si>
-  <si>
-    <t>1.37mm</t>
-  </si>
-  <si>
-    <t>41.176mm</t>
-  </si>
-  <si>
-    <t>C6</t>
-  </si>
-  <si>
-    <t>40.07mm</t>
-  </si>
-  <si>
-    <t>40.615mm</t>
-  </si>
-  <si>
-    <t>C7</t>
-  </si>
-  <si>
-    <t>46.704mm</t>
-  </si>
-  <si>
-    <t>5.347mm</t>
-  </si>
-  <si>
-    <t>46.159mm</t>
-  </si>
-  <si>
-    <t>C8</t>
-  </si>
-  <si>
-    <t>46.699mm</t>
-  </si>
-  <si>
-    <t>4.571mm</t>
-  </si>
-  <si>
-    <t>46.154mm</t>
-  </si>
-  <si>
-    <t>C9</t>
-  </si>
-  <si>
-    <t>40.531mm</t>
-  </si>
-  <si>
-    <t>5.023mm</t>
-  </si>
-  <si>
-    <t>41.076mm</t>
-  </si>
-  <si>
-    <t>C14</t>
-  </si>
-  <si>
-    <t>GRM033R61A104KE15D</t>
-  </si>
-  <si>
-    <t>21.49mm</t>
-  </si>
-  <si>
-    <t>12.4mm</t>
-  </si>
-  <si>
-    <t>21.764mm</t>
-  </si>
-  <si>
-    <t>100nF</t>
-  </si>
-  <si>
-    <t>C15</t>
-  </si>
-  <si>
-    <t>9.4mm</t>
-  </si>
-  <si>
-    <t>C16</t>
-  </si>
-  <si>
-    <t>39.89mm</t>
-  </si>
-  <si>
-    <t>39.616mm</t>
-  </si>
-  <si>
-    <t>C17</t>
-  </si>
-  <si>
-    <t>19.29mm</t>
-  </si>
-  <si>
-    <t>C18</t>
-  </si>
-  <si>
-    <t>11.41mm</t>
-  </si>
-  <si>
-    <t>C19</t>
-  </si>
-  <si>
-    <t>16.17mm</t>
-  </si>
-  <si>
-    <t>C20</t>
-  </si>
-  <si>
-    <t>32.44mm</t>
-  </si>
-  <si>
-    <t>3.6mm</t>
-  </si>
-  <si>
-    <t>3.874mm</t>
-  </si>
-  <si>
-    <t>C21</t>
-  </si>
-  <si>
-    <t>39.49mm</t>
-  </si>
-  <si>
-    <t>6.72mm</t>
-  </si>
-  <si>
-    <t>6.994mm</t>
-  </si>
-  <si>
-    <t>C22</t>
-  </si>
-  <si>
-    <t>29.06mm</t>
-  </si>
-  <si>
-    <t>C23</t>
-  </si>
-  <si>
-    <t>28.99mm</t>
-  </si>
-  <si>
-    <t>22.16mm</t>
-  </si>
-  <si>
-    <t>21.886mm</t>
-  </si>
-  <si>
-    <t>C24</t>
-  </si>
-  <si>
-    <t>28.21mm</t>
-  </si>
-  <si>
-    <t>C25</t>
-  </si>
-  <si>
-    <t>27.43mm</t>
-  </si>
-  <si>
-    <t>C26</t>
-  </si>
-  <si>
-    <t>26.65mm</t>
-  </si>
-  <si>
-    <t>C27</t>
-  </si>
-  <si>
-    <t>13.4mm</t>
-  </si>
-  <si>
-    <t>C28</t>
-  </si>
-  <si>
-    <t>17.01mm</t>
-  </si>
-  <si>
-    <t>C29</t>
-  </si>
-  <si>
-    <t>11.62mm</t>
-  </si>
-  <si>
-    <t>C30</t>
-  </si>
-  <si>
-    <t>10.18mm</t>
-  </si>
-  <si>
-    <t>C31</t>
-  </si>
-  <si>
-    <t>21.48mm</t>
-  </si>
-  <si>
-    <t>6.27mm</t>
-  </si>
-  <si>
-    <t>21.754mm</t>
-  </si>
-  <si>
-    <t>C32</t>
-  </si>
-  <si>
-    <t>30.62mm</t>
-  </si>
-  <si>
-    <t>C33</t>
-  </si>
-  <si>
-    <t>8.62mm</t>
-  </si>
-  <si>
-    <t>C34</t>
-  </si>
-  <si>
-    <t>29.77mm</t>
-  </si>
-  <si>
-    <t>22.12mm</t>
-  </si>
-  <si>
-    <t>21.846mm</t>
-  </si>
-  <si>
-    <t>C37</t>
-  </si>
-  <si>
-    <t>18.51mm</t>
-  </si>
-  <si>
-    <t>C38</t>
-  </si>
-  <si>
-    <t>10.63mm</t>
-  </si>
-  <si>
-    <t>C39</t>
-  </si>
-  <si>
-    <t>21.478mm</t>
-  </si>
-  <si>
-    <t>7.835mm</t>
-  </si>
-  <si>
-    <t>21.753mm</t>
-  </si>
-  <si>
-    <t>C40</t>
-  </si>
-  <si>
-    <t>7.05mm</t>
-  </si>
-  <si>
-    <t>C41</t>
-  </si>
-  <si>
-    <t>23.56mm</t>
-  </si>
-  <si>
-    <t>C44</t>
-  </si>
-  <si>
-    <t>41.08mm</t>
-  </si>
-  <si>
-    <t>17.77mm</t>
-  </si>
-  <si>
-    <t>17.225mm</t>
-  </si>
-  <si>
-    <t>C45</t>
-  </si>
-  <si>
-    <t>16.96mm</t>
-  </si>
-  <si>
-    <t>C46</t>
-  </si>
-  <si>
-    <t>38.24mm</t>
-  </si>
-  <si>
-    <t>5.17mm</t>
-  </si>
-  <si>
-    <t>5.715mm</t>
-  </si>
-  <si>
-    <t>C47</t>
-  </si>
-  <si>
-    <t>41.1mm</t>
-  </si>
-  <si>
-    <t>13.54mm</t>
-  </si>
-  <si>
-    <t>40.555mm</t>
-  </si>
-  <si>
-    <t>C48</t>
-  </si>
-  <si>
-    <t>39.53mm</t>
-  </si>
-  <si>
-    <t>13.53mm</t>
-  </si>
-  <si>
-    <t>13.804mm</t>
-  </si>
-  <si>
-    <t>C49</t>
-  </si>
-  <si>
-    <t>41.12mm</t>
-  </si>
-  <si>
-    <t>15.4mm</t>
-  </si>
-  <si>
-    <t>14.855mm</t>
-  </si>
-  <si>
-    <t>C51</t>
-  </si>
-  <si>
-    <t>25.16mm</t>
-  </si>
-  <si>
-    <t>C52</t>
-  </si>
-  <si>
-    <t>27.5mm</t>
-  </si>
-  <si>
-    <t>C53</t>
-  </si>
-  <si>
-    <t>GRM0335C1H150JA01D</t>
-  </si>
-  <si>
-    <t>22.52mm</t>
-  </si>
-  <si>
-    <t>3.8mm</t>
-  </si>
-  <si>
-    <t>3.526mm</t>
-  </si>
-  <si>
-    <t>15pF</t>
-  </si>
-  <si>
-    <t>C54</t>
-  </si>
-  <si>
-    <t>19.24mm</t>
-  </si>
-  <si>
-    <t>3.83mm</t>
-  </si>
-  <si>
-    <t>3.556mm</t>
-  </si>
-  <si>
-    <t>C55</t>
-  </si>
-  <si>
-    <t>38.01mm</t>
-  </si>
-  <si>
-    <t>1.156mm</t>
-  </si>
-  <si>
-    <t>C56</t>
-  </si>
-  <si>
-    <t>33.84mm</t>
-  </si>
-  <si>
-    <t>C58</t>
-  </si>
-  <si>
-    <t>50.229mm</t>
-  </si>
-  <si>
-    <t>9.93mm</t>
-  </si>
-  <si>
-    <t>9.655mm</t>
-  </si>
-  <si>
-    <t>C59</t>
-  </si>
-  <si>
-    <t>46.7mm</t>
-  </si>
-  <si>
-    <t>6.13mm</t>
-  </si>
-  <si>
-    <t>46.426mm</t>
-  </si>
-  <si>
-    <t>C60</t>
-  </si>
-  <si>
-    <t>10.39mm</t>
-  </si>
-  <si>
-    <t>10.664mm</t>
-  </si>
-  <si>
-    <t>C61</t>
-  </si>
-  <si>
-    <t>14.53mm</t>
-  </si>
-  <si>
-    <t>10.41mm</t>
-  </si>
-  <si>
-    <t>10.684mm</t>
-  </si>
-  <si>
-    <t>C62</t>
-  </si>
-  <si>
-    <t>19.32mm</t>
-  </si>
-  <si>
-    <t>14.39mm</t>
-  </si>
-  <si>
-    <t>19.046mm</t>
-  </si>
-  <si>
-    <t>C63</t>
-  </si>
-  <si>
-    <t>19.33mm</t>
-  </si>
-  <si>
-    <t>17.64mm</t>
-  </si>
-  <si>
-    <t>19.056mm</t>
-  </si>
-  <si>
-    <t>C64</t>
-  </si>
-  <si>
-    <t>14.03mm</t>
-  </si>
-  <si>
-    <t>22.48mm</t>
-  </si>
-  <si>
-    <t>22.206mm</t>
-  </si>
-  <si>
-    <t>C65</t>
-  </si>
-  <si>
-    <t>7.22mm</t>
-  </si>
-  <si>
-    <t>18.14mm</t>
-  </si>
-  <si>
-    <t>7.494mm</t>
-  </si>
-  <si>
-    <t>C66</t>
-  </si>
-  <si>
-    <t>15.7mm</t>
-  </si>
-  <si>
-    <t>C67</t>
-  </si>
-  <si>
-    <t>12.64mm</t>
-  </si>
-  <si>
-    <t>C68</t>
-  </si>
-  <si>
-    <t>C69</t>
-  </si>
-  <si>
-    <t>16.53mm</t>
-  </si>
-  <si>
-    <t>22.46mm</t>
-  </si>
-  <si>
-    <t>22.186mm</t>
-  </si>
-  <si>
-    <t>C70</t>
-  </si>
-  <si>
-    <t>16.48mm</t>
-  </si>
-  <si>
-    <t>C71</t>
-  </si>
-  <si>
-    <t>19.82mm</t>
-  </si>
-  <si>
-    <t>6.71mm</t>
-  </si>
-  <si>
-    <t>6.984mm</t>
-  </si>
-  <si>
-    <t>C72</t>
-  </si>
-  <si>
-    <t>17.83mm</t>
-  </si>
-  <si>
-    <t>8.68mm</t>
-  </si>
-  <si>
-    <t>8.135mm</t>
-  </si>
-  <si>
-    <t>C73</t>
-  </si>
-  <si>
-    <t>6.428mm</t>
-  </si>
-  <si>
-    <t>8.858mm</t>
-  </si>
-  <si>
-    <t>8.313mm</t>
-  </si>
-  <si>
-    <t>C74</t>
-  </si>
-  <si>
-    <t>19.72mm</t>
-  </si>
-  <si>
-    <t>8.94mm</t>
-  </si>
-  <si>
-    <t>8.666mm</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>42.824mm</t>
-  </si>
-  <si>
-    <t>8.537mm</t>
-  </si>
-  <si>
-    <t>43.369mm</t>
-  </si>
-  <si>
-    <t>C10</t>
-  </si>
-  <si>
-    <t>GRM033R61A105ME44D</t>
-  </si>
-  <si>
-    <t>41.014mm</t>
-  </si>
-  <si>
-    <t>5.917mm</t>
-  </si>
-  <si>
-    <t>41.288mm</t>
-  </si>
-  <si>
-    <t>1uF</t>
-  </si>
-  <si>
-    <t>C42</t>
-  </si>
-  <si>
-    <t>24.379mm</t>
-  </si>
-  <si>
-    <t>C43</t>
-  </si>
-  <si>
-    <t>29.84mm</t>
-  </si>
-  <si>
-    <t>C50</t>
-  </si>
-  <si>
-    <t>14.61mm</t>
-  </si>
-  <si>
-    <t>R1</t>
-  </si>
-  <si>
-    <t>0201WMF6802TEE</t>
-  </si>
-  <si>
-    <t>R0201</t>
-  </si>
-  <si>
-    <t>42.329mm</t>
-  </si>
-  <si>
-    <t>7.392mm</t>
-  </si>
-  <si>
-    <t>7.15mm</t>
-  </si>
-  <si>
-    <t>68kΩ</t>
-  </si>
-  <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>0201WMF1502TEE</t>
-  </si>
-  <si>
-    <t>41.539mm</t>
-  </si>
-  <si>
-    <t>15kΩ</t>
-  </si>
-  <si>
-    <t>R3</t>
-  </si>
-  <si>
-    <t>0201WMF2003TEE</t>
-  </si>
-  <si>
-    <t>44.46mm</t>
-  </si>
-  <si>
-    <t>2.2mm</t>
-  </si>
-  <si>
-    <t>44.218mm</t>
-  </si>
-  <si>
-    <t>200kΩ</t>
-  </si>
-  <si>
-    <t>R4</t>
-  </si>
-  <si>
-    <t>0201WMF1003TEE</t>
-  </si>
-  <si>
-    <t>100kΩ</t>
-  </si>
-  <si>
-    <t>R5</t>
-  </si>
-  <si>
-    <t>43.22mm</t>
-  </si>
-  <si>
-    <t>43.461mm</t>
-  </si>
-  <si>
-    <t>R6</t>
-  </si>
-  <si>
-    <t>R7</t>
-  </si>
-  <si>
-    <t>0201WMF0000TEE</t>
-  </si>
-  <si>
-    <t>8.04mm</t>
-  </si>
-  <si>
-    <t>7.798mm</t>
-  </si>
-  <si>
-    <t>0Ω</t>
-  </si>
-  <si>
-    <t>R8</t>
-  </si>
-  <si>
-    <t>0201WMF2400TEE</t>
-  </si>
-  <si>
-    <t>28.28mm</t>
-  </si>
-  <si>
-    <t>3.665mm</t>
-  </si>
-  <si>
-    <t>3.907mm</t>
-  </si>
-  <si>
-    <t>240Ω</t>
-  </si>
-  <si>
-    <t>R9</t>
-  </si>
-  <si>
-    <t>15.39mm</t>
-  </si>
-  <si>
-    <t>40.131mm</t>
-  </si>
-  <si>
-    <t>R10</t>
-  </si>
-  <si>
-    <t>0201WMF2001TEE</t>
-  </si>
-  <si>
-    <t>25.94mm</t>
-  </si>
-  <si>
-    <t>2kΩ</t>
-  </si>
-  <si>
-    <t>R11</t>
-  </si>
-  <si>
-    <t>26.72mm</t>
-  </si>
-  <si>
-    <t>3.424mm</t>
-  </si>
-  <si>
-    <t>R12</t>
-  </si>
-  <si>
-    <t>0201WMF1005TEE</t>
-  </si>
-  <si>
-    <t>36.65mm</t>
-  </si>
-  <si>
-    <t>3.89mm</t>
-  </si>
-  <si>
-    <t>36.408mm</t>
-  </si>
-  <si>
-    <t>10MΩ</t>
-  </si>
-  <si>
-    <t>R13</t>
-  </si>
-  <si>
-    <t>0201WMF4702TEE</t>
-  </si>
-  <si>
-    <t>48.54mm</t>
-  </si>
-  <si>
-    <t>19.13mm</t>
-  </si>
-  <si>
-    <t>18.888mm</t>
-  </si>
-  <si>
-    <t>47kΩ</t>
-  </si>
-  <si>
-    <t>R14</t>
-  </si>
-  <si>
-    <t>51.77mm</t>
-  </si>
-  <si>
-    <t>18.08mm</t>
-  </si>
-  <si>
-    <t>18.322mm</t>
-  </si>
-  <si>
-    <t>R15</t>
-  </si>
-  <si>
-    <t>17.67mm</t>
-  </si>
-  <si>
-    <t>17.428mm</t>
-  </si>
-  <si>
-    <t>R16</t>
-  </si>
-  <si>
-    <t>48.38mm</t>
-  </si>
-  <si>
-    <t>14.31mm</t>
-  </si>
-  <si>
-    <t>14.068mm</t>
-  </si>
-  <si>
-    <t>R17</t>
-  </si>
-  <si>
-    <t>51.07mm</t>
-  </si>
-  <si>
-    <t>13.24mm</t>
-  </si>
-  <si>
-    <t>13.482mm</t>
-  </si>
-  <si>
-    <t>R18</t>
-  </si>
-  <si>
-    <t>0201WMF330JTEE</t>
-  </si>
-  <si>
-    <t>51.21mm</t>
-  </si>
-  <si>
-    <t>16.87mm</t>
-  </si>
-  <si>
-    <t>51.451mm</t>
-  </si>
-  <si>
-    <t>33Ω</t>
-  </si>
-  <si>
-    <t>R19</t>
-  </si>
-  <si>
-    <t>0201WMF4701TEE</t>
-  </si>
-  <si>
-    <t>11.84mm</t>
-  </si>
-  <si>
-    <t>19.078mm</t>
-  </si>
-  <si>
-    <t>4.7kΩ</t>
-  </si>
-  <si>
-    <t>R20</t>
-  </si>
-  <si>
-    <t>12.62mm</t>
-  </si>
-  <si>
-    <t>R21</t>
-  </si>
-  <si>
-    <t>0201WMF2201TEE</t>
-  </si>
-  <si>
-    <t>7.285mm</t>
-  </si>
-  <si>
-    <t>14.92mm</t>
-  </si>
-  <si>
-    <t>7.527mm</t>
-  </si>
-  <si>
-    <t>2.2kΩ</t>
-  </si>
-  <si>
-    <t>R22</t>
-  </si>
-  <si>
-    <t>14.14mm</t>
-  </si>
-  <si>
-    <t>R23</t>
-  </si>
-  <si>
-    <t>0201WMF4301TEE</t>
-  </si>
-  <si>
-    <t>9.79mm</t>
-  </si>
-  <si>
-    <t>10.58mm</t>
-  </si>
-  <si>
-    <t>9.548mm</t>
-  </si>
-  <si>
-    <t>4.3kΩ</t>
-  </si>
-  <si>
-    <t>R24</t>
-  </si>
-  <si>
-    <t>0201WMF1002TEE</t>
-  </si>
-  <si>
-    <t>11.86mm</t>
-  </si>
-  <si>
-    <t>10kΩ</t>
-  </si>
-  <si>
-    <t>R25</t>
-  </si>
-  <si>
-    <t>17.843mm</t>
-  </si>
-  <si>
-    <t>10.453mm</t>
-  </si>
-  <si>
-    <t>10.694mm</t>
-  </si>
-  <si>
-    <t>R26</t>
-  </si>
-  <si>
-    <t>0201WMF5101TEE</t>
-  </si>
-  <si>
-    <t>52.107mm</t>
-  </si>
-  <si>
-    <t>7.729mm</t>
-  </si>
-  <si>
-    <t>7.97mm</t>
-  </si>
-  <si>
-    <t>5.1kΩ</t>
-  </si>
-  <si>
-    <t>R27</t>
-  </si>
-  <si>
-    <t>55.098mm</t>
-  </si>
-  <si>
-    <t>R36</t>
-  </si>
-  <si>
-    <t>0201WMF220JTEE</t>
-  </si>
-  <si>
-    <t>41.52mm</t>
-  </si>
-  <si>
-    <t>12.44mm</t>
-  </si>
-  <si>
-    <t>41.761mm</t>
-  </si>
-  <si>
-    <t>22Ω</t>
-  </si>
-  <si>
-    <t>R37</t>
-  </si>
-  <si>
-    <t>11.65mm</t>
-  </si>
-  <si>
-    <t>3V0</t>
-  </si>
-  <si>
-    <t>43.692mm</t>
-  </si>
-  <si>
-    <t>14.362mm</t>
-  </si>
-  <si>
-    <t>C82</t>
-  </si>
-  <si>
-    <t>46.88mm</t>
-  </si>
-  <si>
-    <t>14.25mm</t>
-  </si>
-  <si>
-    <t>13.976mm</t>
-  </si>
-  <si>
-    <t>C83</t>
-  </si>
-  <si>
-    <t>42.18mm</t>
-  </si>
-  <si>
-    <t>14.95mm</t>
-  </si>
-  <si>
-    <t>14.676mm</t>
-  </si>
-  <si>
-    <t>U9</t>
-  </si>
-  <si>
-    <t>LP5907MFX-3.3/NOPB</t>
-  </si>
-  <si>
-    <t>SOT-23-5_L3.0-W1.7-P0.95-LS2.8-BR</t>
-  </si>
-  <si>
-    <t>44.54mm</t>
-  </si>
-  <si>
-    <t>14.7mm</t>
-  </si>
-  <si>
-    <t>45.84mm</t>
-  </si>
-  <si>
-    <t>13.75mm</t>
+    <t>18.373mm</t>
+  </si>
+  <si>
+    <t>IOV</t>
+  </si>
+  <si>
+    <t>7.314mm</t>
+  </si>
+  <si>
+    <t>10.479mm</t>
+  </si>
+  <si>
+    <t>61.644mm</t>
+  </si>
+  <si>
+    <t>16.178mm</t>
+  </si>
+  <si>
+    <t>13.958mm</t>
+  </si>
+  <si>
+    <t>RST</t>
+  </si>
+  <si>
+    <t>40.334mm</t>
+  </si>
+  <si>
+    <t>8.003mm</t>
   </si>
 </sst>
 </file>
@@ -1998,7 +2067,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N135"/>
+  <dimension ref="A1:N146"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="14" width="20" customWidth="1"/>
@@ -6767,22 +6836,22 @@
         <v>398</v>
       </c>
       <c r="D109" t="s">
-        <v>234</v>
+        <v>422</v>
       </c>
       <c r="E109" t="s">
+        <v>423</v>
+      </c>
+      <c r="F109" t="s">
         <v>422</v>
       </c>
-      <c r="F109" t="s">
-        <v>234</v>
-      </c>
       <c r="G109" t="s">
+        <v>423</v>
+      </c>
+      <c r="H109" t="s">
         <v>422</v>
       </c>
-      <c r="H109" t="s">
-        <v>234</v>
-      </c>
       <c r="I109" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="J109">
         <v>2</v>
@@ -6791,43 +6860,43 @@
         <v>21</v>
       </c>
       <c r="L109">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="M109" t="s">
         <v>30</v>
       </c>
       <c r="N109" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B110" t="s">
-        <v>426</v>
+        <v>408</v>
       </c>
       <c r="C110" t="s">
         <v>398</v>
       </c>
       <c r="D110" t="s">
+        <v>221</v>
+      </c>
+      <c r="E110" t="s">
         <v>427</v>
       </c>
-      <c r="E110" t="s">
+      <c r="F110" t="s">
+        <v>221</v>
+      </c>
+      <c r="G110" t="s">
+        <v>427</v>
+      </c>
+      <c r="H110" t="s">
         <v>428</v>
       </c>
-      <c r="F110" t="s">
+      <c r="I110" t="s">
         <v>427</v>
       </c>
-      <c r="G110" t="s">
-        <v>428</v>
-      </c>
-      <c r="H110" t="s">
-        <v>427</v>
-      </c>
-      <c r="I110" t="s">
-        <v>429</v>
-      </c>
       <c r="J110">
         <v>2</v>
       </c>
@@ -6835,86 +6904,86 @@
         <v>21</v>
       </c>
       <c r="L110">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="M110" t="s">
         <v>30</v>
       </c>
       <c r="N110" t="s">
-        <v>430</v>
+        <v>412</v>
       </c>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B111" t="s">
-        <v>408</v>
+        <v>430</v>
       </c>
       <c r="C111" t="s">
         <v>398</v>
       </c>
       <c r="D111" t="s">
-        <v>221</v>
+        <v>431</v>
       </c>
       <c r="E111" t="s">
+        <v>423</v>
+      </c>
+      <c r="F111" t="s">
+        <v>431</v>
+      </c>
+      <c r="G111" t="s">
+        <v>423</v>
+      </c>
+      <c r="H111" t="s">
+        <v>431</v>
+      </c>
+      <c r="I111" t="s">
+        <v>424</v>
+      </c>
+      <c r="J111">
+        <v>2</v>
+      </c>
+      <c r="K111" t="s">
+        <v>21</v>
+      </c>
+      <c r="L111">
+        <v>270</v>
+      </c>
+      <c r="M111" t="s">
+        <v>30</v>
+      </c>
+      <c r="N111" t="s">
         <v>432</v>
-      </c>
-      <c r="F111" t="s">
-        <v>221</v>
-      </c>
-      <c r="G111" t="s">
-        <v>432</v>
-      </c>
-      <c r="H111" t="s">
-        <v>433</v>
-      </c>
-      <c r="I111" t="s">
-        <v>432</v>
-      </c>
-      <c r="J111">
-        <v>2</v>
-      </c>
-      <c r="K111" t="s">
-        <v>21</v>
-      </c>
-      <c r="L111">
-        <v>180</v>
-      </c>
-      <c r="M111" t="s">
-        <v>30</v>
-      </c>
-      <c r="N111" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B112" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="C112" t="s">
         <v>398</v>
       </c>
       <c r="D112" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E112" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="F112" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="G112" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="H112" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="I112" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="J112">
         <v>2</v>
@@ -6923,43 +6992,43 @@
         <v>21</v>
       </c>
       <c r="L112">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="M112" t="s">
         <v>30</v>
       </c>
       <c r="N112" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B113" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C113" t="s">
         <v>398</v>
       </c>
       <c r="D113" t="s">
+        <v>438</v>
+      </c>
+      <c r="E113" t="s">
         <v>439</v>
       </c>
-      <c r="E113" t="s">
-        <v>428</v>
-      </c>
       <c r="F113" t="s">
+        <v>438</v>
+      </c>
+      <c r="G113" t="s">
         <v>439</v>
       </c>
-      <c r="G113" t="s">
-        <v>428</v>
-      </c>
       <c r="H113" t="s">
+        <v>440</v>
+      </c>
+      <c r="I113" t="s">
         <v>439</v>
       </c>
-      <c r="I113" t="s">
-        <v>440</v>
-      </c>
       <c r="J113">
         <v>2</v>
       </c>
@@ -6967,42 +7036,42 @@
         <v>21</v>
       </c>
       <c r="L113">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M113" t="s">
         <v>30</v>
       </c>
       <c r="N113" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B114" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C114" t="s">
         <v>398</v>
       </c>
       <c r="D114" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E114" t="s">
+        <v>445</v>
+      </c>
+      <c r="F114" t="s">
         <v>444</v>
       </c>
-      <c r="F114" t="s">
-        <v>443</v>
-      </c>
       <c r="G114" t="s">
+        <v>445</v>
+      </c>
+      <c r="H114" t="s">
         <v>444</v>
       </c>
-      <c r="H114" t="s">
-        <v>445</v>
-      </c>
       <c r="I114" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="J114">
         <v>2</v>
@@ -7011,21 +7080,21 @@
         <v>21</v>
       </c>
       <c r="L114">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M114" t="s">
         <v>30</v>
       </c>
       <c r="N114" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B115" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="C115" t="s">
         <v>398</v>
@@ -7055,43 +7124,43 @@
         <v>21</v>
       </c>
       <c r="L115">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="M115" t="s">
         <v>30</v>
       </c>
       <c r="N115" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B116" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="C116" t="s">
         <v>398</v>
       </c>
       <c r="D116" t="s">
+        <v>444</v>
+      </c>
+      <c r="E116" t="s">
+        <v>453</v>
+      </c>
+      <c r="F116" t="s">
+        <v>444</v>
+      </c>
+      <c r="G116" t="s">
+        <v>453</v>
+      </c>
+      <c r="H116" t="s">
+        <v>444</v>
+      </c>
+      <c r="I116" t="s">
         <v>454</v>
       </c>
-      <c r="E116" t="s">
-        <v>455</v>
-      </c>
-      <c r="F116" t="s">
-        <v>454</v>
-      </c>
-      <c r="G116" t="s">
-        <v>455</v>
-      </c>
-      <c r="H116" t="s">
-        <v>454</v>
-      </c>
-      <c r="I116" t="s">
-        <v>456</v>
-      </c>
       <c r="J116">
         <v>2</v>
       </c>
@@ -7099,42 +7168,42 @@
         <v>21</v>
       </c>
       <c r="L116">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="M116" t="s">
         <v>30</v>
       </c>
       <c r="N116" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B117" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="C117" t="s">
         <v>398</v>
       </c>
       <c r="D117" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="E117" t="s">
+        <v>457</v>
+      </c>
+      <c r="F117" t="s">
+        <v>456</v>
+      </c>
+      <c r="G117" t="s">
+        <v>457</v>
+      </c>
+      <c r="H117" t="s">
+        <v>456</v>
+      </c>
+      <c r="I117" t="s">
         <v>458</v>
-      </c>
-      <c r="F117" t="s">
-        <v>449</v>
-      </c>
-      <c r="G117" t="s">
-        <v>458</v>
-      </c>
-      <c r="H117" t="s">
-        <v>449</v>
-      </c>
-      <c r="I117" t="s">
-        <v>459</v>
       </c>
       <c r="J117">
         <v>2</v>
@@ -7149,37 +7218,37 @@
         <v>30</v>
       </c>
       <c r="N117" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B118" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="C118" t="s">
         <v>398</v>
       </c>
       <c r="D118" t="s">
+        <v>460</v>
+      </c>
+      <c r="E118" t="s">
         <v>461</v>
       </c>
-      <c r="E118" t="s">
+      <c r="F118" t="s">
+        <v>460</v>
+      </c>
+      <c r="G118" t="s">
+        <v>461</v>
+      </c>
+      <c r="H118" t="s">
+        <v>460</v>
+      </c>
+      <c r="I118" t="s">
         <v>462</v>
       </c>
-      <c r="F118" t="s">
-        <v>461</v>
-      </c>
-      <c r="G118" t="s">
-        <v>462</v>
-      </c>
-      <c r="H118" t="s">
-        <v>461</v>
-      </c>
-      <c r="I118" t="s">
-        <v>463</v>
-      </c>
       <c r="J118">
         <v>2</v>
       </c>
@@ -7187,21 +7256,21 @@
         <v>21</v>
       </c>
       <c r="L118">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="M118" t="s">
         <v>30</v>
       </c>
       <c r="N118" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>463</v>
+      </c>
+      <c r="B119" t="s">
         <v>464</v>
-      </c>
-      <c r="B119" t="s">
-        <v>448</v>
       </c>
       <c r="C119" t="s">
         <v>398</v>
@@ -7219,10 +7288,10 @@
         <v>466</v>
       </c>
       <c r="H119" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="I119" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="J119">
         <v>2</v>
@@ -7231,33 +7300,33 @@
         <v>21</v>
       </c>
       <c r="L119">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="M119" t="s">
         <v>30</v>
       </c>
       <c r="N119" t="s">
-        <v>452</v>
+        <v>468</v>
       </c>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B120" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C120" t="s">
         <v>398</v>
       </c>
       <c r="D120" t="s">
-        <v>470</v>
+        <v>338</v>
       </c>
       <c r="E120" t="s">
         <v>471</v>
       </c>
       <c r="F120" t="s">
-        <v>470</v>
+        <v>338</v>
       </c>
       <c r="G120" t="s">
         <v>471</v>
@@ -7275,7 +7344,7 @@
         <v>21</v>
       </c>
       <c r="L120">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M120" t="s">
         <v>30</v>
@@ -7289,7 +7358,7 @@
         <v>474</v>
       </c>
       <c r="B121" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="C121" t="s">
         <v>398</v>
@@ -7298,19 +7367,19 @@
         <v>338</v>
       </c>
       <c r="E121" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F121" t="s">
         <v>338</v>
       </c>
       <c r="G121" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H121" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="I121" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="J121">
         <v>2</v>
@@ -7325,36 +7394,36 @@
         <v>30</v>
       </c>
       <c r="N121" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="B122" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C122" t="s">
         <v>398</v>
       </c>
       <c r="D122" t="s">
-        <v>338</v>
+        <v>478</v>
       </c>
       <c r="E122" t="s">
+        <v>479</v>
+      </c>
+      <c r="F122" t="s">
+        <v>478</v>
+      </c>
+      <c r="G122" t="s">
+        <v>479</v>
+      </c>
+      <c r="H122" t="s">
         <v>480</v>
       </c>
-      <c r="F122" t="s">
-        <v>338</v>
-      </c>
-      <c r="G122" t="s">
-        <v>480</v>
-      </c>
-      <c r="H122" t="s">
-        <v>477</v>
-      </c>
       <c r="I122" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J122">
         <v>2</v>
@@ -7363,42 +7432,42 @@
         <v>21</v>
       </c>
       <c r="L122">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M122" t="s">
         <v>30</v>
       </c>
       <c r="N122" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B123" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="C123" t="s">
         <v>398</v>
       </c>
       <c r="D123" t="s">
+        <v>478</v>
+      </c>
+      <c r="E123" t="s">
         <v>483</v>
       </c>
-      <c r="E123" t="s">
-        <v>484</v>
-      </c>
       <c r="F123" t="s">
+        <v>478</v>
+      </c>
+      <c r="G123" t="s">
         <v>483</v>
       </c>
-      <c r="G123" t="s">
-        <v>484</v>
-      </c>
       <c r="H123" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="I123" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="J123">
         <v>2</v>
@@ -7413,36 +7482,36 @@
         <v>30</v>
       </c>
       <c r="N123" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B124" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C124" t="s">
         <v>398</v>
       </c>
       <c r="D124" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="E124" t="s">
+        <v>487</v>
+      </c>
+      <c r="F124" t="s">
+        <v>486</v>
+      </c>
+      <c r="G124" t="s">
+        <v>487</v>
+      </c>
+      <c r="H124" t="s">
         <v>488</v>
       </c>
-      <c r="F124" t="s">
-        <v>483</v>
-      </c>
-      <c r="G124" t="s">
-        <v>488</v>
-      </c>
-      <c r="H124" t="s">
-        <v>485</v>
-      </c>
       <c r="I124" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="J124">
         <v>2</v>
@@ -7451,39 +7520,39 @@
         <v>21</v>
       </c>
       <c r="L124">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M124" t="s">
         <v>30</v>
       </c>
       <c r="N124" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B125" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C125" t="s">
         <v>398</v>
       </c>
       <c r="D125" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="E125" t="s">
         <v>492</v>
       </c>
       <c r="F125" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="G125" t="s">
         <v>492</v>
       </c>
       <c r="H125" t="s">
-        <v>493</v>
+        <v>480</v>
       </c>
       <c r="I125" t="s">
         <v>492</v>
@@ -7495,39 +7564,39 @@
         <v>21</v>
       </c>
       <c r="L125">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M125" t="s">
         <v>30</v>
       </c>
       <c r="N125" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B126" t="s">
-        <v>496</v>
+        <v>470</v>
       </c>
       <c r="C126" t="s">
         <v>398</v>
       </c>
       <c r="D126" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="E126" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F126" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="G126" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H126" t="s">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="I126" t="s">
         <v>497</v>
@@ -7539,21 +7608,21 @@
         <v>21</v>
       </c>
       <c r="L126">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="M126" t="s">
         <v>30</v>
       </c>
       <c r="N126" t="s">
-        <v>498</v>
+        <v>473</v>
       </c>
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
+        <v>498</v>
+      </c>
+      <c r="B127" t="s">
         <v>499</v>
-      </c>
-      <c r="B127" t="s">
-        <v>475</v>
       </c>
       <c r="C127" t="s">
         <v>398</v>
@@ -7589,15 +7658,15 @@
         <v>30</v>
       </c>
       <c r="N127" t="s">
-        <v>478</v>
+        <v>503</v>
       </c>
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B128" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="C128" t="s">
         <v>398</v>
@@ -7606,19 +7675,19 @@
         <v>505</v>
       </c>
       <c r="E128" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="F128" t="s">
         <v>505</v>
       </c>
       <c r="G128" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="H128" t="s">
         <v>505</v>
       </c>
       <c r="I128" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="J128">
         <v>2</v>
@@ -7633,36 +7702,36 @@
         <v>30</v>
       </c>
       <c r="N128" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="B129" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C129" t="s">
         <v>398</v>
       </c>
       <c r="D129" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="E129" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="F129" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="G129" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="H129" t="s">
         <v>510</v>
       </c>
       <c r="I129" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="J129">
         <v>2</v>
@@ -7671,42 +7740,42 @@
         <v>21</v>
       </c>
       <c r="L129">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="M129" t="s">
         <v>30</v>
       </c>
       <c r="N129" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B130" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="C130" t="s">
         <v>398</v>
       </c>
       <c r="D130" t="s">
+        <v>508</v>
+      </c>
+      <c r="E130" t="s">
         <v>513</v>
       </c>
-      <c r="E130" t="s">
-        <v>514</v>
-      </c>
       <c r="F130" t="s">
+        <v>508</v>
+      </c>
+      <c r="G130" t="s">
         <v>513</v>
       </c>
-      <c r="G130" t="s">
-        <v>514</v>
-      </c>
       <c r="H130" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="I130" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="J130">
         <v>2</v>
@@ -7721,42 +7790,42 @@
         <v>30</v>
       </c>
       <c r="N130" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="B131" t="s">
-        <v>512</v>
+        <v>150</v>
       </c>
       <c r="C131" t="s">
-        <v>398</v>
+        <v>151</v>
       </c>
       <c r="D131" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E131" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="F131" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="G131" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H131" t="s">
         <v>515</v>
       </c>
       <c r="I131" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="J131">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K131" t="s">
-        <v>21</v>
+        <v>154</v>
       </c>
       <c r="L131">
         <v>180</v>
@@ -7765,56 +7834,56 @@
         <v>30</v>
       </c>
       <c r="N131" t="s">
-        <v>516</v>
+        <v>150</v>
       </c>
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
+        <v>517</v>
+      </c>
+      <c r="B132" t="s">
+        <v>385</v>
+      </c>
+      <c r="C132" t="s">
+        <v>177</v>
+      </c>
+      <c r="D132" t="s">
+        <v>518</v>
+      </c>
+      <c r="E132" t="s">
         <v>519</v>
       </c>
-      <c r="B132" t="s">
-        <v>150</v>
-      </c>
-      <c r="C132" t="s">
-        <v>151</v>
-      </c>
-      <c r="D132" t="s">
+      <c r="F132" t="s">
+        <v>518</v>
+      </c>
+      <c r="G132" t="s">
+        <v>519</v>
+      </c>
+      <c r="H132" t="s">
+        <v>518</v>
+      </c>
+      <c r="I132" t="s">
         <v>520</v>
       </c>
-      <c r="E132" t="s">
-        <v>521</v>
-      </c>
-      <c r="F132" t="s">
-        <v>520</v>
-      </c>
-      <c r="G132" t="s">
-        <v>521</v>
-      </c>
-      <c r="H132" t="s">
-        <v>520</v>
-      </c>
-      <c r="I132" t="s">
-        <v>521</v>
-      </c>
       <c r="J132">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K132" t="s">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="L132">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="M132" t="s">
         <v>30</v>
       </c>
       <c r="N132" t="s">
-        <v>150</v>
+        <v>389</v>
       </c>
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B133" t="s">
         <v>385</v>
@@ -7823,22 +7892,22 @@
         <v>177</v>
       </c>
       <c r="D133" t="s">
+        <v>522</v>
+      </c>
+      <c r="E133" t="s">
         <v>523</v>
       </c>
-      <c r="E133" t="s">
+      <c r="F133" t="s">
+        <v>522</v>
+      </c>
+      <c r="G133" t="s">
+        <v>523</v>
+      </c>
+      <c r="H133" t="s">
+        <v>522</v>
+      </c>
+      <c r="I133" t="s">
         <v>524</v>
-      </c>
-      <c r="F133" t="s">
-        <v>523</v>
-      </c>
-      <c r="G133" t="s">
-        <v>524</v>
-      </c>
-      <c r="H133" t="s">
-        <v>523</v>
-      </c>
-      <c r="I133" t="s">
-        <v>525</v>
       </c>
       <c r="J133">
         <v>2</v>
@@ -7858,57 +7927,57 @@
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
+        <v>525</v>
+      </c>
+      <c r="B134" t="s">
         <v>526</v>
       </c>
-      <c r="B134" t="s">
-        <v>385</v>
-      </c>
       <c r="C134" t="s">
-        <v>177</v>
+        <v>527</v>
       </c>
       <c r="D134" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E134" t="s">
+        <v>529</v>
+      </c>
+      <c r="F134" t="s">
         <v>528</v>
       </c>
-      <c r="F134" t="s">
-        <v>527</v>
-      </c>
       <c r="G134" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H134" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="I134" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="J134">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K134" t="s">
         <v>21</v>
       </c>
       <c r="L134">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="M134" t="s">
         <v>30</v>
       </c>
       <c r="N134" t="s">
-        <v>389</v>
+        <v>526</v>
       </c>
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B135" t="s">
-        <v>531</v>
+        <v>150</v>
       </c>
       <c r="C135" t="s">
-        <v>532</v>
+        <v>151</v>
       </c>
       <c r="D135" t="s">
         <v>533</v>
@@ -7923,25 +7992,509 @@
         <v>534</v>
       </c>
       <c r="H135" t="s">
+        <v>533</v>
+      </c>
+      <c r="I135" t="s">
+        <v>534</v>
+      </c>
+      <c r="J135">
+        <v>1</v>
+      </c>
+      <c r="K135" t="s">
+        <v>154</v>
+      </c>
+      <c r="L135">
+        <v>180</v>
+      </c>
+      <c r="M135" t="s">
+        <v>30</v>
+      </c>
+      <c r="N135" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
         <v>535</v>
       </c>
-      <c r="I135" t="s">
+      <c r="B136" t="s">
+        <v>150</v>
+      </c>
+      <c r="C136" t="s">
+        <v>151</v>
+      </c>
+      <c r="D136" t="s">
+        <v>50</v>
+      </c>
+      <c r="E136" t="s">
         <v>536</v>
       </c>
-      <c r="J135">
-        <v>5</v>
-      </c>
-      <c r="K135" t="s">
-        <v>21</v>
-      </c>
-      <c r="L135">
-        <v>0</v>
-      </c>
-      <c r="M135" t="s">
-        <v>30</v>
-      </c>
-      <c r="N135" t="s">
-        <v>531</v>
+      <c r="F136" t="s">
+        <v>50</v>
+      </c>
+      <c r="G136" t="s">
+        <v>536</v>
+      </c>
+      <c r="H136" t="s">
+        <v>50</v>
+      </c>
+      <c r="I136" t="s">
+        <v>536</v>
+      </c>
+      <c r="J136">
+        <v>1</v>
+      </c>
+      <c r="K136" t="s">
+        <v>154</v>
+      </c>
+      <c r="L136">
+        <v>180</v>
+      </c>
+      <c r="M136" t="s">
+        <v>30</v>
+      </c>
+      <c r="N136" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>537</v>
+      </c>
+      <c r="B137" t="s">
+        <v>150</v>
+      </c>
+      <c r="C137" t="s">
+        <v>151</v>
+      </c>
+      <c r="D137" t="s">
+        <v>50</v>
+      </c>
+      <c r="E137" t="s">
+        <v>538</v>
+      </c>
+      <c r="F137" t="s">
+        <v>50</v>
+      </c>
+      <c r="G137" t="s">
+        <v>538</v>
+      </c>
+      <c r="H137" t="s">
+        <v>50</v>
+      </c>
+      <c r="I137" t="s">
+        <v>538</v>
+      </c>
+      <c r="J137">
+        <v>1</v>
+      </c>
+      <c r="K137" t="s">
+        <v>154</v>
+      </c>
+      <c r="L137">
+        <v>180</v>
+      </c>
+      <c r="M137" t="s">
+        <v>30</v>
+      </c>
+      <c r="N137" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>539</v>
+      </c>
+      <c r="B138" t="s">
+        <v>150</v>
+      </c>
+      <c r="C138" t="s">
+        <v>151</v>
+      </c>
+      <c r="D138" t="s">
+        <v>540</v>
+      </c>
+      <c r="E138" t="s">
+        <v>541</v>
+      </c>
+      <c r="F138" t="s">
+        <v>540</v>
+      </c>
+      <c r="G138" t="s">
+        <v>541</v>
+      </c>
+      <c r="H138" t="s">
+        <v>540</v>
+      </c>
+      <c r="I138" t="s">
+        <v>541</v>
+      </c>
+      <c r="J138">
+        <v>1</v>
+      </c>
+      <c r="K138" t="s">
+        <v>154</v>
+      </c>
+      <c r="L138">
+        <v>180</v>
+      </c>
+      <c r="M138" t="s">
+        <v>30</v>
+      </c>
+      <c r="N138" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>542</v>
+      </c>
+      <c r="B139" t="s">
+        <v>150</v>
+      </c>
+      <c r="C139" t="s">
+        <v>151</v>
+      </c>
+      <c r="D139" t="s">
+        <v>50</v>
+      </c>
+      <c r="E139" t="s">
+        <v>543</v>
+      </c>
+      <c r="F139" t="s">
+        <v>50</v>
+      </c>
+      <c r="G139" t="s">
+        <v>543</v>
+      </c>
+      <c r="H139" t="s">
+        <v>50</v>
+      </c>
+      <c r="I139" t="s">
+        <v>543</v>
+      </c>
+      <c r="J139">
+        <v>1</v>
+      </c>
+      <c r="K139" t="s">
+        <v>154</v>
+      </c>
+      <c r="L139">
+        <v>180</v>
+      </c>
+      <c r="M139" t="s">
+        <v>30</v>
+      </c>
+      <c r="N139" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>544</v>
+      </c>
+      <c r="B140" t="s">
+        <v>150</v>
+      </c>
+      <c r="C140" t="s">
+        <v>151</v>
+      </c>
+      <c r="D140" t="s">
+        <v>50</v>
+      </c>
+      <c r="E140" t="s">
+        <v>545</v>
+      </c>
+      <c r="F140" t="s">
+        <v>50</v>
+      </c>
+      <c r="G140" t="s">
+        <v>545</v>
+      </c>
+      <c r="H140" t="s">
+        <v>50</v>
+      </c>
+      <c r="I140" t="s">
+        <v>545</v>
+      </c>
+      <c r="J140">
+        <v>1</v>
+      </c>
+      <c r="K140" t="s">
+        <v>154</v>
+      </c>
+      <c r="L140">
+        <v>180</v>
+      </c>
+      <c r="M140" t="s">
+        <v>30</v>
+      </c>
+      <c r="N140" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>546</v>
+      </c>
+      <c r="B141" t="s">
+        <v>150</v>
+      </c>
+      <c r="C141" t="s">
+        <v>151</v>
+      </c>
+      <c r="D141" t="s">
+        <v>547</v>
+      </c>
+      <c r="E141" t="s">
+        <v>548</v>
+      </c>
+      <c r="F141" t="s">
+        <v>547</v>
+      </c>
+      <c r="G141" t="s">
+        <v>548</v>
+      </c>
+      <c r="H141" t="s">
+        <v>547</v>
+      </c>
+      <c r="I141" t="s">
+        <v>548</v>
+      </c>
+      <c r="J141">
+        <v>1</v>
+      </c>
+      <c r="K141" t="s">
+        <v>154</v>
+      </c>
+      <c r="L141">
+        <v>180</v>
+      </c>
+      <c r="M141" t="s">
+        <v>30</v>
+      </c>
+      <c r="N141" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>549</v>
+      </c>
+      <c r="B142" t="s">
+        <v>150</v>
+      </c>
+      <c r="C142" t="s">
+        <v>151</v>
+      </c>
+      <c r="D142" t="s">
+        <v>50</v>
+      </c>
+      <c r="E142" t="s">
+        <v>550</v>
+      </c>
+      <c r="F142" t="s">
+        <v>50</v>
+      </c>
+      <c r="G142" t="s">
+        <v>550</v>
+      </c>
+      <c r="H142" t="s">
+        <v>50</v>
+      </c>
+      <c r="I142" t="s">
+        <v>550</v>
+      </c>
+      <c r="J142">
+        <v>1</v>
+      </c>
+      <c r="K142" t="s">
+        <v>154</v>
+      </c>
+      <c r="L142">
+        <v>180</v>
+      </c>
+      <c r="M142" t="s">
+        <v>30</v>
+      </c>
+      <c r="N142" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>551</v>
+      </c>
+      <c r="B143" t="s">
+        <v>150</v>
+      </c>
+      <c r="C143" t="s">
+        <v>151</v>
+      </c>
+      <c r="D143" t="s">
+        <v>552</v>
+      </c>
+      <c r="E143" t="s">
+        <v>553</v>
+      </c>
+      <c r="F143" t="s">
+        <v>552</v>
+      </c>
+      <c r="G143" t="s">
+        <v>553</v>
+      </c>
+      <c r="H143" t="s">
+        <v>552</v>
+      </c>
+      <c r="I143" t="s">
+        <v>553</v>
+      </c>
+      <c r="J143">
+        <v>1</v>
+      </c>
+      <c r="K143" t="s">
+        <v>154</v>
+      </c>
+      <c r="L143">
+        <v>180</v>
+      </c>
+      <c r="M143" t="s">
+        <v>30</v>
+      </c>
+      <c r="N143" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>158</v>
+      </c>
+      <c r="B144" t="s">
+        <v>150</v>
+      </c>
+      <c r="C144" t="s">
+        <v>151</v>
+      </c>
+      <c r="D144" t="s">
+        <v>554</v>
+      </c>
+      <c r="E144" t="s">
+        <v>555</v>
+      </c>
+      <c r="F144" t="s">
+        <v>554</v>
+      </c>
+      <c r="G144" t="s">
+        <v>555</v>
+      </c>
+      <c r="H144" t="s">
+        <v>554</v>
+      </c>
+      <c r="I144" t="s">
+        <v>555</v>
+      </c>
+      <c r="J144">
+        <v>1</v>
+      </c>
+      <c r="K144" t="s">
+        <v>154</v>
+      </c>
+      <c r="L144">
+        <v>180</v>
+      </c>
+      <c r="M144" t="s">
+        <v>30</v>
+      </c>
+      <c r="N144" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>167</v>
+      </c>
+      <c r="B145" t="s">
+        <v>150</v>
+      </c>
+      <c r="C145" t="s">
+        <v>151</v>
+      </c>
+      <c r="D145" t="s">
+        <v>554</v>
+      </c>
+      <c r="E145" t="s">
+        <v>556</v>
+      </c>
+      <c r="F145" t="s">
+        <v>554</v>
+      </c>
+      <c r="G145" t="s">
+        <v>556</v>
+      </c>
+      <c r="H145" t="s">
+        <v>554</v>
+      </c>
+      <c r="I145" t="s">
+        <v>556</v>
+      </c>
+      <c r="J145">
+        <v>1</v>
+      </c>
+      <c r="K145" t="s">
+        <v>154</v>
+      </c>
+      <c r="L145">
+        <v>180</v>
+      </c>
+      <c r="M145" t="s">
+        <v>30</v>
+      </c>
+      <c r="N145" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>557</v>
+      </c>
+      <c r="B146" t="s">
+        <v>150</v>
+      </c>
+      <c r="C146" t="s">
+        <v>151</v>
+      </c>
+      <c r="D146" t="s">
+        <v>558</v>
+      </c>
+      <c r="E146" t="s">
+        <v>559</v>
+      </c>
+      <c r="F146" t="s">
+        <v>558</v>
+      </c>
+      <c r="G146" t="s">
+        <v>559</v>
+      </c>
+      <c r="H146" t="s">
+        <v>558</v>
+      </c>
+      <c r="I146" t="s">
+        <v>559</v>
+      </c>
+      <c r="J146">
+        <v>1</v>
+      </c>
+      <c r="K146" t="s">
+        <v>154</v>
+      </c>
+      <c r="L146">
+        <v>180</v>
+      </c>
+      <c r="M146" t="s">
+        <v>30</v>
+      </c>
+      <c r="N146" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>
